--- a/public/build/assets/templates/Format Import Data Keuangan.xlsx
+++ b/public/build/assets/templates/Format Import Data Keuangan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyek Akhir\sim-almanaar\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99E9134-1BD1-44A3-AFDB-E2AB5A93929E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C8121F-BD9E-405E-ACE1-5E4A4EB2DE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{1376679D-98CA-4C2A-A6F0-47AFD37B426B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{1376679D-98CA-4C2A-A6F0-47AFD37B426B}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA IMPORT" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
   <si>
     <t>Kategori Kas</t>
   </si>
@@ -327,6 +327,9 @@
   <si>
     <t>Bencana</t>
   </si>
+  <si>
+    <t>26.8.23</t>
+  </si>
 </sst>
 </file>
 
@@ -335,7 +338,7 @@
   <numFmts count="1">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,6 +369,12 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -437,6 +446,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -445,9 +457,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -854,38 +863,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="166.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="9" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
@@ -1904,7 +1914,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data Tidak Valid" error="Maaf, Anda harus memilih data yang tersedia dari daftar dropdown." sqref="B5:B101" xr:uid="{4965D169-6584-4CE5-BC20-811152BA1718}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data Tidak Valid" error="Maaf, Anda harus memilih data yang tersedia dari daftar dropdown." sqref="B6:B101 B5" xr:uid="{4965D169-6584-4CE5-BC20-811152BA1718}">
       <formula1>INDIRECT(SUBSTITUTE($B$4, " ", "_"))</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data Tidak Valid" error="Maaf, Anda harus memilih data yang tersedia dari daftar dropdown." sqref="C5:C101" xr:uid="{A999C142-9FA7-426D-AC79-E838D777D292}">
